--- a/BioStarsGPT-HumanTesting.xlsx
+++ b/BioStarsGPT-HumanTesting.xlsx
@@ -8,24 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\munee\OneDrive\Desktop\Projects\BioStarsGPT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCA7880-AA35-4F21-9C8C-D391FE120FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707DFAF0-7C5A-468F-82BF-5F72D1FC559B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BioStarGPT" sheetId="1" r:id="rId1"/>
+    <sheet name="Google Studio" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="69">
   <si>
     <t>Questions</t>
   </si>
@@ -366,13 +378,72 @@
   <si>
     <t>Response was verfied from ChatGPT.</t>
   </si>
+  <si>
+    <t>My Score (out of 5)</t>
+  </si>
+  <si>
+    <t>Correct. The model accurately diagnoses the problem as a PLINK version mismatch. The error unknown option '--bed' is a classic sign of using a PLINK 1.x version with PLINK 2.0 flags. The advice to check the version and upgrade is the perfect solution.</t>
+  </si>
+  <si>
+    <t>Correct. The provided two-step pipeline (VCF to PLINK format, then run --genome) is a standard and correct workflow for calculating IBS/IBD. The explanation of the flags and output files is also accurate.</t>
+  </si>
+  <si>
+    <t>Correct. The model correctly identifies that the IDlist.txt for PLINK's --remove flag requires two columns: Family ID (FID) and Individual ID (IID). Providing only one column causes the error. The given solution is accurate.</t>
+  </si>
+  <si>
+    <t>Incorrect. The model provides a PLINK2 command with a non-existent flag (--fws). This is a 'hallucination' and would cause the command to fail. While it correctly identifies relevant tools (PLINK2, LDpred), providing a fake command is a critical error.</t>
+  </si>
+  <si>
+    <t>Mostly Correct. The core command for running an association test with an external phenotype file is correct. However, the response is structured poorly (listing two redundant commands) and includes irrelevant flags (--ld-snp, --ld-window-kb) that are confusing in the context of a 'simple association test'.</t>
+  </si>
+  <si>
+    <t>Correct. Your assessment of 'Cannot be verified' is inaccurate. The model's answer is perfectly correct. The ClassCastException from String to Boolean in Hail is a common data type error, and the solution ht.is_case.cast('bool') is the exact, standard way to fix it.</t>
+  </si>
+  <si>
+    <t>Correct. The model provides a good, high-level conceptual overview of a standard GWAS pipeline (QC -&gt; Imputation -&gt; Pruning -&gt; Analysis). It names appropriate tools for each step. For a general 'how-to' question, this is a solid answer.</t>
+  </si>
+  <si>
+    <t>Correct. Your comment mentions bcftools, but the model correctly recommended bedtools intersect, which is the canonical tool for this job. The provided command and explanation of the flags are perfect.</t>
+  </si>
+  <si>
+    <t>Partially Correct. The choice of review papers is excellent for a beginner. However, two of the four links are malformed and broken. Providing non-functional links for a resource-based question is a significant flaw.</t>
+  </si>
+  <si>
+    <t>Incorrect. Your assessment is spot-on. The model fundamentally misunderstands the concept. The 'null model' in PRS analysis includes covariates without the PRS. The null R² is the variance explained by covariates alone. The model's explanation is wrong and misleading.</t>
+  </si>
+  <si>
+    <t>Incorrect. The answer is vague and contains a hallucinated command. The flag --export pgs does not exist in PLINK2. The answer fails to address the most critical step: reformatting the PGS Catalog file into a format usable by PRSice-2 or PLINK.</t>
+  </si>
+  <si>
+    <t>Incorrect. The model invents a command-line syntax for LDpred2, which is an R package and does not use the syntax shown. This is highly misleading. While it correctly mentions the need for a reference panel, the core of the answer (the command) is a fabrication.</t>
+  </si>
+  <si>
+    <t>Correct. The model gives a perfect conceptual explanation of how to create covariate and phenotype files from UK Biobank data. It correctly identifies what information goes into each file and the importance of sample alignment.</t>
+  </si>
+  <si>
+    <t>Correct. This is an excellent, comprehensive, and responsible answer. It correctly identifies the workflow (use external GWAS summary stats), recommends the right tools, and importantly, provides strong caveats about the severe limitations of calculating a PRS on only two individuals.</t>
+  </si>
+  <si>
+    <t>Correct. The model correctly identifies data sparsity as a primary reason for a lack of specificity in scRNA-seq ligand-receptor analysis. This is a well-known challenge in the field and a direct, accurate explanation for the user's observation.</t>
+  </si>
+  <si>
+    <t>Gemini Model's Answer</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -402,7 +473,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -683,13 +754,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="43.109375" customWidth="1"/>
+    <col min="9" max="9" width="26.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,15 +780,24 @@
       <c r="F1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
@@ -725,15 +806,24 @@
       <c r="F2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
@@ -742,15 +832,24 @@
       <c r="F3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
@@ -759,15 +858,24 @@
       <c r="F4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>18</v>
       </c>
       <c r="E5" t="s">
@@ -776,169 +884,258 @@
       <c r="F5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>6</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>7</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>26</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>8</v>
       </c>
       <c r="C9" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>30</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>9</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>33</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>10</v>
       </c>
       <c r="C11" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>36</v>
       </c>
       <c r="E11" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>11</v>
       </c>
       <c r="C12" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>40</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>12</v>
       </c>
       <c r="C13" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>42</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>13</v>
       </c>
       <c r="C14" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" t="s">
         <v>7</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J14" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>14</v>
       </c>
       <c r="C15" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>48</v>
       </c>
       <c r="E15" t="s">
@@ -947,15 +1144,24 @@
       <c r="F15" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>15</v>
       </c>
       <c r="C16" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>49</v>
       </c>
       <c r="E16" t="s">
@@ -963,9 +1169,33 @@
       </c>
       <c r="F16" t="s">
         <v>51</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J17">
+        <f>SUM(J2:J16)/15</f>
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D775F4-CF28-4A93-8CD8-C9A0EAB70ED1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>